--- a/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/自动化UI测试需要用到的测试用例3.20/品牌管理/新增品牌.xlsx
+++ b/快乐羊毛系统/功能测试需要的文件2026.03.17/最终版测试用例/自动化UI测试需要用到的测试用例3.20/品牌管理/新增品牌.xlsx
@@ -709,7 +709,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,13 +727,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -884,7 +877,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -894,6 +887,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1208,157 +1207,160 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1733,7 +1735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:5">
+    <row r="2" ht="35" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1750,7 +1752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:5">
+    <row r="3" ht="35" customHeight="1" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1767,7 +1769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5">
+    <row r="4" ht="35" customHeight="1" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1784,7 +1786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:5">
+    <row r="5" ht="35" customHeight="1" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1801,7 +1803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:5">
+    <row r="6" ht="35" customHeight="1" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -1818,7 +1820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:5">
+    <row r="7" ht="35" customHeight="1" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1835,7 +1837,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="1:5">
+    <row r="8" ht="35" customHeight="1" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1852,11 +1854,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="1:5">
+    <row r="9" ht="35" customHeight="1" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1869,11 +1871,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1" spans="1:5">
+    <row r="10" ht="35" customHeight="1" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1886,7 +1888,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1" spans="1:5">
+    <row r="11" ht="35" customHeight="1" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
@@ -1903,7 +1905,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5">
+    <row r="12" ht="35" customHeight="1" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -1920,7 +1922,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" spans="1:5">
+    <row r="13" ht="35" customHeight="1" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -1937,7 +1939,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" spans="1:5">
+    <row r="14" ht="35" customHeight="1" spans="1:5">
       <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
@@ -1954,7 +1956,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1" spans="1:5">
+    <row r="15" ht="35" customHeight="1" spans="1:5">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -1971,7 +1973,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1" spans="1:5">
+    <row r="16" ht="35" customHeight="1" spans="1:5">
       <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
@@ -1988,7 +1990,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5">
+    <row r="17" ht="35" customHeight="1" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
@@ -2005,7 +2007,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1" spans="1:5">
+    <row r="18" ht="35" customHeight="1" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>61</v>
       </c>
@@ -2022,7 +2024,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1" spans="1:5">
+    <row r="19" ht="35" customHeight="1" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>61</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1" spans="1:5">
+    <row r="20" ht="35" customHeight="1" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>68</v>
       </c>
@@ -2056,7 +2058,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1" spans="1:5">
+    <row r="21" ht="35" customHeight="1" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -2073,7 +2075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1" spans="1:5">
+    <row r="22" ht="35" customHeight="1" spans="1:5">
       <c r="A22" s="2" t="s">
         <v>75</v>
       </c>
@@ -2090,7 +2092,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="1:5">
+    <row r="23" ht="35" customHeight="1" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>75</v>
       </c>
@@ -2107,7 +2109,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1" spans="1:5">
+    <row r="24" ht="35" customHeight="1" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>75</v>
       </c>
@@ -2124,7 +2126,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1" spans="1:5">
+    <row r="25" ht="35" customHeight="1" spans="1:5">
       <c r="A25" s="2" t="s">
         <v>75</v>
       </c>
@@ -2141,7 +2143,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1" spans="1:5">
+    <row r="26" ht="35" customHeight="1" spans="1:5">
       <c r="A26" s="2" t="s">
         <v>75</v>
       </c>
@@ -2158,7 +2160,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1" spans="1:5">
+    <row r="27" ht="35" customHeight="1" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>75</v>
       </c>
@@ -2175,7 +2177,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1" spans="1:5">
+    <row r="28" ht="35" customHeight="1" spans="1:5">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -2192,7 +2194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1" spans="1:5">
+    <row r="29" ht="35" customHeight="1" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>94</v>
       </c>
@@ -2209,7 +2211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1" spans="1:5">
+    <row r="30" ht="35" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>101</v>
       </c>
@@ -2226,7 +2228,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1" spans="1:5">
+    <row r="31" ht="35" customHeight="1" spans="1:5">
       <c r="A31" s="2" t="s">
         <v>101</v>
       </c>
@@ -2243,7 +2245,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1" spans="1:5">
+    <row r="32" ht="35" customHeight="1" spans="1:5">
       <c r="A32" s="2" t="s">
         <v>101</v>
       </c>
@@ -2260,11 +2262,11 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1" spans="1:5">
+    <row r="33" ht="35" customHeight="1" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2277,11 +2279,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1" spans="1:5">
+    <row r="34" ht="35" customHeight="1" spans="1:5">
       <c r="A34" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -2294,7 +2296,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1" spans="1:5">
+    <row r="35" ht="35" customHeight="1" spans="1:5">
       <c r="A35" s="2" t="s">
         <v>111</v>
       </c>
@@ -2311,7 +2313,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1" spans="1:5">
+    <row r="36" ht="35" customHeight="1" spans="1:5">
       <c r="A36" s="2" t="s">
         <v>111</v>
       </c>
@@ -2328,7 +2330,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1" spans="1:5">
+    <row r="37" ht="35" customHeight="1" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>127</v>
       </c>
@@ -2345,7 +2347,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1" spans="1:5">
+    <row r="38" ht="35" customHeight="1" spans="1:5">
       <c r="A38" s="2" t="s">
         <v>127</v>
       </c>
@@ -2362,7 +2364,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1" spans="1:5">
+    <row r="39" ht="35" customHeight="1" spans="1:5">
       <c r="A39" s="2" t="s">
         <v>135</v>
       </c>
@@ -2379,7 +2381,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1" spans="1:5">
+    <row r="40" ht="35" customHeight="1" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>135</v>
       </c>
@@ -2396,7 +2398,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1" spans="1:5">
+    <row r="41" ht="35" customHeight="1" spans="1:5">
       <c r="A41" s="2" t="s">
         <v>143</v>
       </c>
@@ -2413,7 +2415,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1" spans="1:5">
+    <row r="42" ht="35" customHeight="1" spans="1:5">
       <c r="A42" s="2" t="s">
         <v>143</v>
       </c>
@@ -2430,7 +2432,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1" spans="1:5">
+    <row r="43" ht="35" customHeight="1" spans="1:5">
       <c r="A43" s="2" t="s">
         <v>143</v>
       </c>
@@ -2447,7 +2449,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1" spans="1:5">
+    <row r="44" ht="35" customHeight="1" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>153</v>
       </c>
@@ -2464,7 +2466,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1" spans="1:5">
+    <row r="45" ht="35" customHeight="1" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>153</v>
       </c>
@@ -2481,7 +2483,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1" spans="1:5">
+    <row r="46" ht="35" customHeight="1" spans="1:5">
       <c r="A46" s="2" t="s">
         <v>160</v>
       </c>
@@ -2498,7 +2500,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1" spans="1:5">
+    <row r="47" ht="35" customHeight="1" spans="1:5">
       <c r="A47" s="2" t="s">
         <v>160</v>
       </c>
@@ -2515,7 +2517,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1" spans="1:5">
+    <row r="48" ht="35" customHeight="1" spans="1:5">
       <c r="A48" s="2" t="s">
         <v>160</v>
       </c>
